--- a/research/traditional_assets/database/data/finland/finland_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0207</v>
+        <v>0.0009700000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.28</v>
+        <v>0.0363</v>
       </c>
       <c r="F2">
-        <v>0.0599</v>
+        <v>0.0462</v>
       </c>
       <c r="G2">
-        <v>0.2690677966101695</v>
+        <v>0.1832871119328249</v>
       </c>
       <c r="H2">
-        <v>0.2690677966101695</v>
+        <v>0.1832871119328249</v>
       </c>
       <c r="I2">
-        <v>0.1572151600753296</v>
+        <v>0.1959017024882521</v>
       </c>
       <c r="J2">
-        <v>0.1233822029847133</v>
+        <v>0.1523200009058262</v>
       </c>
       <c r="K2">
-        <v>340.8</v>
+        <v>1511.3</v>
       </c>
       <c r="L2">
-        <v>0.04011299435028249</v>
+        <v>0.1455300053924967</v>
       </c>
       <c r="M2">
-        <v>1257.4</v>
+        <v>1351.7</v>
       </c>
       <c r="N2">
-        <v>0.05723285039986527</v>
+        <v>0.06159629975620315</v>
       </c>
       <c r="O2">
-        <v>3.689553990610329</v>
+        <v>0.8943955534969894</v>
       </c>
       <c r="P2">
-        <v>269.9</v>
+        <v>1007.1</v>
       </c>
       <c r="Q2">
-        <v>0.0122849899180242</v>
+        <v>0.04589304837202944</v>
       </c>
       <c r="R2">
-        <v>0.7919600938967135</v>
+        <v>0.6663799378018924</v>
       </c>
       <c r="S2">
-        <v>987.5000000000001</v>
+        <v>344.6</v>
       </c>
       <c r="T2">
-        <v>0.7853507237156037</v>
+        <v>0.2549382259377081</v>
       </c>
       <c r="U2">
-        <v>1440.5</v>
+        <v>1666.3</v>
       </c>
       <c r="V2">
-        <v>0.06556698027756157</v>
+        <v>0.07593246599375697</v>
       </c>
       <c r="W2">
-        <v>0.03860793909733551</v>
+        <v>0.210414201183432</v>
       </c>
       <c r="X2">
-        <v>0.07671704087762861</v>
+        <v>0.08178264280767361</v>
       </c>
       <c r="Y2">
-        <v>-0.0381091017802931</v>
+        <v>0.1286315583757583</v>
       </c>
       <c r="Z2">
-        <v>0.8853689037098791</v>
+        <v>1.194190499189292</v>
       </c>
       <c r="AA2">
-        <v>0.1092387657938854</v>
+        <v>0.181899097918242</v>
       </c>
       <c r="AB2">
-        <v>0.07273246373334874</v>
+        <v>0.07720019932533687</v>
       </c>
       <c r="AC2">
-        <v>0.03650630206053664</v>
+        <v>0.1046988985929051</v>
       </c>
       <c r="AD2">
-        <v>2954.1</v>
+        <v>3286.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2954.1</v>
+        <v>3286.9</v>
       </c>
       <c r="AG2">
-        <v>1513.6</v>
+        <v>1620.6</v>
       </c>
       <c r="AH2">
-        <v>0.1185243139142995</v>
+        <v>0.1302702188542847</v>
       </c>
       <c r="AI2">
-        <v>0.2791574530815898</v>
+        <v>0.2932663567662095</v>
       </c>
       <c r="AJ2">
-        <v>0.06445376540975578</v>
+        <v>0.0687711912956024</v>
       </c>
       <c r="AK2">
-        <v>0.1655709550740015</v>
+        <v>0.1698457281797602</v>
       </c>
       <c r="AL2">
-        <v>111.1</v>
+        <v>109.3</v>
       </c>
       <c r="AM2">
-        <v>111.1</v>
+        <v>109.3</v>
       </c>
       <c r="AN2">
-        <v>2.003594682582746</v>
+        <v>1.484665070689733</v>
       </c>
       <c r="AO2">
-        <v>12.02250225022502</v>
+        <v>18.61299176578225</v>
       </c>
       <c r="AP2">
-        <v>1.026587086272382</v>
+        <v>0.7320113826279416</v>
       </c>
       <c r="AQ2">
-        <v>12.02250225022502</v>
+        <v>18.61299176578225</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0207</v>
+        <v>0.0009700000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.28</v>
+        <v>0.0363</v>
       </c>
       <c r="F3">
-        <v>0.0599</v>
+        <v>0.0462</v>
       </c>
       <c r="G3">
-        <v>0.2690677966101695</v>
+        <v>0.1832871119328249</v>
       </c>
       <c r="H3">
-        <v>0.2690677966101695</v>
+        <v>0.1832871119328249</v>
       </c>
       <c r="I3">
-        <v>0.1572151600753296</v>
+        <v>0.1959017024882521</v>
       </c>
       <c r="J3">
-        <v>0.1233822029847133</v>
+        <v>0.1523200009058262</v>
       </c>
       <c r="K3">
-        <v>340.8</v>
+        <v>1511.3</v>
       </c>
       <c r="L3">
-        <v>0.04011299435028249</v>
+        <v>0.1455300053924967</v>
       </c>
       <c r="M3">
-        <v>1257.4</v>
+        <v>1351.7</v>
       </c>
       <c r="N3">
-        <v>0.05723285039986527</v>
+        <v>0.06159629975620315</v>
       </c>
       <c r="O3">
-        <v>3.689553990610329</v>
+        <v>0.8943955534969894</v>
       </c>
       <c r="P3">
-        <v>269.9</v>
+        <v>1007.1</v>
       </c>
       <c r="Q3">
-        <v>0.0122849899180242</v>
+        <v>0.04589304837202944</v>
       </c>
       <c r="R3">
-        <v>0.7919600938967135</v>
+        <v>0.6663799378018924</v>
       </c>
       <c r="S3">
-        <v>987.5000000000001</v>
+        <v>344.6</v>
       </c>
       <c r="T3">
-        <v>0.7853507237156037</v>
+        <v>0.2549382259377081</v>
       </c>
       <c r="U3">
-        <v>1440.5</v>
+        <v>1666.3</v>
       </c>
       <c r="V3">
-        <v>0.06556698027756157</v>
+        <v>0.07593246599375697</v>
       </c>
       <c r="W3">
-        <v>0.03860793909733551</v>
+        <v>0.210414201183432</v>
       </c>
       <c r="X3">
-        <v>0.07671704087762861</v>
+        <v>0.08178264280767361</v>
       </c>
       <c r="Y3">
-        <v>-0.0381091017802931</v>
+        <v>0.1286315583757583</v>
       </c>
       <c r="Z3">
-        <v>0.8853689037098791</v>
+        <v>1.194190499189292</v>
       </c>
       <c r="AA3">
-        <v>0.1092387657938854</v>
+        <v>0.181899097918242</v>
       </c>
       <c r="AB3">
-        <v>0.07273246373334874</v>
+        <v>0.07720019932533687</v>
       </c>
       <c r="AC3">
-        <v>0.03650630206053664</v>
+        <v>0.1046988985929051</v>
       </c>
       <c r="AD3">
-        <v>2954.1</v>
+        <v>3286.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2954.1</v>
+        <v>3286.9</v>
       </c>
       <c r="AG3">
-        <v>1513.6</v>
+        <v>1620.6</v>
       </c>
       <c r="AH3">
-        <v>0.1185243139142995</v>
+        <v>0.1302702188542847</v>
       </c>
       <c r="AI3">
-        <v>0.2791574530815898</v>
+        <v>0.2932663567662095</v>
       </c>
       <c r="AJ3">
-        <v>0.06445376540975578</v>
+        <v>0.0687711912956024</v>
       </c>
       <c r="AK3">
-        <v>0.1655709550740015</v>
+        <v>0.1698457281797602</v>
       </c>
       <c r="AL3">
-        <v>111.1</v>
+        <v>109.3</v>
       </c>
       <c r="AM3">
-        <v>111.1</v>
+        <v>109.3</v>
       </c>
       <c r="AN3">
-        <v>2.003594682582746</v>
+        <v>1.484665070689733</v>
       </c>
       <c r="AO3">
-        <v>12.02250225022502</v>
+        <v>18.61299176578225</v>
       </c>
       <c r="AP3">
-        <v>1.026587086272382</v>
+        <v>0.7320113826279416</v>
       </c>
       <c r="AQ3">
-        <v>12.02250225022502</v>
+        <v>18.61299176578225</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_insurance_prop_cas.xlsx
@@ -648,10 +648,10 @@
         <v>0.210414201183432</v>
       </c>
       <c r="X2">
-        <v>0.08178264280767361</v>
+        <v>0.08176395998748839</v>
       </c>
       <c r="Y2">
-        <v>0.1286315583757583</v>
+        <v>0.1286502411959436</v>
       </c>
       <c r="Z2">
         <v>1.194190499189292</v>
@@ -660,10 +660,10 @@
         <v>0.181899097918242</v>
       </c>
       <c r="AB2">
-        <v>0.07720019932533687</v>
+        <v>0.077183950320226</v>
       </c>
       <c r="AC2">
-        <v>0.1046988985929051</v>
+        <v>0.104715147598016</v>
       </c>
       <c r="AD2">
         <v>3286.9</v>
@@ -785,10 +785,10 @@
         <v>0.210414201183432</v>
       </c>
       <c r="X3">
-        <v>0.08178264280767361</v>
+        <v>0.08176395998748839</v>
       </c>
       <c r="Y3">
-        <v>0.1286315583757583</v>
+        <v>0.1286502411959436</v>
       </c>
       <c r="Z3">
         <v>1.194190499189292</v>
@@ -797,10 +797,10 @@
         <v>0.181899097918242</v>
       </c>
       <c r="AB3">
-        <v>0.07720019932533687</v>
+        <v>0.077183950320226</v>
       </c>
       <c r="AC3">
-        <v>0.1046988985929051</v>
+        <v>0.104715147598016</v>
       </c>
       <c r="AD3">
         <v>3286.9</v>
